--- a/mode_docx_gen/pmi_ka/ka_modes/КА_31.xlsx
+++ b/mode_docx_gen/pmi_ka/ka_modes/КА_31.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>SGF13_lvalh</t>
         </is>
       </c>
     </row>
@@ -653,11 +653,11 @@
       <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -806,16 +806,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1</v>
@@ -1089,8 +1089,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1155,8 +1155,8 @@
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" s="2" t="n">
-        <v>1</v>
+      <c r="W2" t="n">
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1173,17 +1173,17 @@
       <c r="AB2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
+      <c r="AC2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>1</v>
+      <c r="AE2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1469,16 +1469,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1529,19 +1529,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1569,9 +1569,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1584,34 +1584,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1619,9 +1619,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1639,9 +1639,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1659,9 +1659,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
